--- a/artfynd/A 55409-2024 artfynd.xlsx
+++ b/artfynd/A 55409-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1984466</v>
+        <v>154295</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>693488.3223280413</v>
+        <v>693525</v>
       </c>
       <c r="R2" t="n">
-        <v>7152140.075698922</v>
+        <v>7152149</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2011-11-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-11-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +760,7 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1984467</v>
+        <v>120421652</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,37 +787,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>NV Lillsele, Vb</t>
+          <t>Vinbergsmyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>693503.8298720813</v>
+        <v>693715</v>
       </c>
       <c r="R3" t="n">
-        <v>7152121.141481809</v>
+        <v>7151921</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2011-11-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2011-11-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,31 +861,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Anna Hallmén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Naturvärdesbedömning</t>
-        </is>
-      </c>
+          <t>Anna Hallmén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>154295</v>
+        <v>120421650</v>
       </c>
       <c r="B4" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,37 +884,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>NV Lillsele, Vb</t>
+          <t>Vinbergsmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>693525.4511445556</v>
+        <v>693641</v>
       </c>
       <c r="R4" t="n">
-        <v>7152149.358451218</v>
+        <v>7151931</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,22 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2011-11-08</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2011-11-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,31 +958,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Anna Hallmén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Caspar Ström</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Naturvärdesbedömning</t>
-        </is>
-      </c>
+          <t>Anna Hallmén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120421652</v>
+        <v>120421653</v>
       </c>
       <c r="B5" t="n">
-        <v>89704</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>693715</v>
+        <v>693693</v>
       </c>
       <c r="R5" t="n">
-        <v>7151921</v>
+        <v>7151928</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1128,12 +1070,7 @@
         <v>120421651</v>
       </c>
       <c r="B6" t="n">
-        <v>91923</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1227,53 +1164,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120421653</v>
+        <v>1859151</v>
       </c>
       <c r="B7" t="n">
-        <v>91913</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vinbergsmyran, Vb</t>
+          <t>NV Lillsele, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>693693</v>
+        <v>693670</v>
       </c>
       <c r="R7" t="n">
-        <v>7151928</v>
+        <v>7152195</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,12 +1234,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2011-11-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2011-11-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,27 +1254,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna Hallmén</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna Hallmén</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120421650</v>
+        <v>1984466</v>
       </c>
       <c r="B8" t="n">
-        <v>91913</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1345,37 +1281,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vinbergsmyran, Vb</t>
+          <t>NV Lillsele, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>693641</v>
+        <v>693488</v>
       </c>
       <c r="R8" t="n">
-        <v>7151931</v>
+        <v>7152140</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1399,12 +1335,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2011-11-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2011-11-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1419,15 +1355,221 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna Hallmén</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna Hallmén</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1984467</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>NV Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>693504</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7152121</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2011-11-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2011-11-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniella Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1984468</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>NV Lillsele, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>693662</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7152195</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2011-11-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2011-11-08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniella Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturvärdesbedömning</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55409-2024 artfynd.xlsx
+++ b/artfynd/A 55409-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesbedömning</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/154295</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120421652</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120421650</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120421653</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120421651</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1267,6 +1297,11 @@
           <t>Naturvärdesbedömning</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1859151</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1368,6 +1403,11 @@
           <t>Naturvärdesbedömning</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1984466</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1469,6 +1509,11 @@
           <t>Naturvärdesbedömning</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1984467</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1570,8 +1615,24 @@
           <t>Naturvärdesbedömning</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1984468</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>